--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>44651</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44970</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>45181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45061</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45035</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45660</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>46191</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44595</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>46029</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>46261</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44701</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>46021</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>46213</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44651</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>45208</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4573,10 +4573,10 @@
         <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>46202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44551</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>46089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44482</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45853</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45966</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45758</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>46121</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45379</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44662</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45905</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45294</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45142</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45966</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45965</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>46029</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>46071</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>45160</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>46101</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45632</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44468</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>46188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>46188</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>46191</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46247</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46253</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>46211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45964</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45818</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45849</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>46089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44788</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44950</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45133</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44846</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45973</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>46003</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46010</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>46171</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>46051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>46054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45722</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>46111</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46127</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>46134</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44937</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45741</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45310</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>46213</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46280</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45573</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45818</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44463</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44713</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44516</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>44715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44515</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44481</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>44579</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44580</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44708</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>44708</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44824</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44504</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44627</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44790</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44469</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44517</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>44859</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44551</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>44865</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44704</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44701</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>44648</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44648</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44491</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44469</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>44636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44672</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44469</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44631</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>44728</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44749</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44627</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44627</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44819</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45252</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45252</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>44965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>44491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45580</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45080</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45685</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44847</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44907</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45005</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44704</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45253</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45173</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45394</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44620</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45189</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45224</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45622</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45447</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44769</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45022</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44841</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44853</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44739</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45161</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45541</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44638</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45478</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45399</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>44966</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45649</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45539</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45162</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44603</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>44858</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45401</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45030</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44945</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44735</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44518</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45772</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44942</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45526</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44916</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45393</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44965</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45987</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>45936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45868</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45950</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45807</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44865</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>44704</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44704</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45736</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45812</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45138</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45121</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45770</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44887</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45852</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45275</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>46139</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45852</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45847</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45894</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45390</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>46139</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>44670</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45796</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44843</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45685</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45735</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45632</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45901</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45763</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45901</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45901</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45901</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45741</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>46028</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45852</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45538</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45748</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45637</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>44964</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45908</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45908</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45265</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45910</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45911</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45226</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44972</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>44684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45492</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>46141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45623</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45786</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45841</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44896</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44896</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44928</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>44953</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45917</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45853</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45845</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45489</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45912</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45489</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45071</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45587</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45912</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45666</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45786</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45853</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>44936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45623</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46029</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45921</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45922</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44964</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45922</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45921</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45922</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45184</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44984</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45928</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45057</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45926</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45635</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45312</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46146</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45936</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45936</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45936</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45936</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45936</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45259</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45330</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45320</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45937</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46147</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>46148</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46148</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46148</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45763</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46148</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46148</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45296</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45947</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45946</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46148</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45222</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46153</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45957</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45954</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45954</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45958</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44956</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45959</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44600</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46153</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44689</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45965</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45965</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46155</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45966</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>46154</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>45637</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45973</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45972</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45973</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45973</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45973</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45973</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45979</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44858</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46155</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45982</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45982</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45439</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45987</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45632</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45960</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45257</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45239</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46161</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45469</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45989</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46030</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45991</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45957</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45748</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44726</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46160</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44732</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>44966</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>44909</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45994</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45994</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>45999</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>44853</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45574</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>46000</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45961</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45961</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46003</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46002</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46002</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>46002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46002</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>46007</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45677</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>46009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>46008</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>46008</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>46010</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>46010</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>46010</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>46010</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46014</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>46017</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45751</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>45951</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45910</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45783</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45911</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45040</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45891</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>46020</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>46027</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44781</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>46153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>45400</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>44713</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46030</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44781</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46170</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46171</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>46034</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44978</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>46036</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44594</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44964</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>44747</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>46042</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46043</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45181</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45865</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46048</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46048</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>46051</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>46051</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46051</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>46051</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>46051</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>46051</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>44909</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46176</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45366</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>46055</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46055</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>46053</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>46053</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46052</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46052</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>46053</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>46055</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45560</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>46177</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45135</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45229</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>44978</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>46181</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46076</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45761</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45058</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46076</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46183</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>44956</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45639</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>46079</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>44908</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44971</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46044</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46070</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45470</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46055</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>44597</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>46188</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>46084</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>45580</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>44874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>46084</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>46185</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>44701</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46091</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>46190</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46190</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46190</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>46191</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>46191</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>46098</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46100</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>46100</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>46196</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45244</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>46195</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>46196</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>46195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>46104</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>46196</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>46195</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46196</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45190</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45385</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44696</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46108</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>46108</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>46108</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46111</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>46199</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>46244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>46119</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45439</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46202</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46126</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>46127</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45387</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45387</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>46127</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>46127</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>46127</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>46125</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45314</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46204</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>44792</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45762</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45104</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>46134</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>46134</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45072</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>46134</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>46134</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>46134</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>46134</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45804</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>46071</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>46126</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45655</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45824</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45992</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45833</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45748</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46203</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>46248</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>46248</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>46248</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46248</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>46248</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>46248</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>45174</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>44980</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>44981</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
         <v>44750</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>46206</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>46252</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>46252</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>46210</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>46252</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45439</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>44732</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>46254</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>46254</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51632,7 +51632,7 @@
         <v>46212</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>46211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45204</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45754</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>46212</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>46213</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45075</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>46257</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>46213</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>46253</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>46257</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>46213</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>44883</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>46260</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>46265</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45167</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>44917</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>44804</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45046</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45392</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>46262</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>46262</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46265</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45448</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>46219</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>46266</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45762</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45727</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>46266</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45092</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45390</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
         <v>45033</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>45638</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54296,7 +54296,7 @@
         <v>46268</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45776</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45516</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45308</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45357</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46272</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>46230</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>46275</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>45785</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45527</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55041,7 +55041,7 @@
         <v>45791</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>46280</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>46282</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45119</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45203</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45511</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         <v>46239</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55572,7 +55572,7 @@
         <v>45645</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45526</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>45799</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45387</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45366</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>45645</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>45343</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56098,7 +56098,7 @@
         <v>45446</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45851</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45812</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45852</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45851</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45851</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45785</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45867</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45868</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45852</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45792</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>45526</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45638</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45315</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>44585</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>45432</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>45035</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>45805</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>45982</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45660</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46262</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44651</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44970</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>45181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45061</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45035</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45660</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>46191</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44579</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44595</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>46261</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46021</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44651</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45208</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>45722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>46089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44482</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45379</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45966</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44804</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45335</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45310</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>46101</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>45294</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45142</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45160</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44662</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45548</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45632</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45399</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44862</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44468</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45849</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46191</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>46253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>46247</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>46089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44579</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44827</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44756</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44788</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45573</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45621</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>46051</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>46054</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45741</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44950</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>45748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>46111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46127</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45674</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45973</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>46134</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44937</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45789</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>46003</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46010</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45133</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>46148</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46161</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45310</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>46280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45722</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>44978</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44656</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45784</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44587</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44837</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>44560</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44516</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44515</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44481</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44580</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44708</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44886</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44504</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44790</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44469</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>44734</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44480</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44859</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44551</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44865</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44581</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44543</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44704</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>44788</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44648</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44648</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44469</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>44491</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44636</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44469</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44631</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44728</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>44627</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44781</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45387</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>44792</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45033</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45253</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45330</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>44841</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44853</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45748</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>44916</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45763</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44837</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45439</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44858</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44858</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45763</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45511</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>46014</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45040</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45119</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>46017</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45783</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45951</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45910</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46020</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45203</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>46027</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46030</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>44853</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45492</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46036</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46042</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45685</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45894</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46042</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45896</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>46042</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46043</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45539</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45901</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45901</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45538</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46048</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45902</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45645</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45645</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45901</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>45901</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>46048</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45393</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45138</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>46051</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45908</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45908</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46052</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46051</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46051</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46052</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45526</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>46053</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46055</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45366</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44964</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45400</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45909</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>46053</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46053</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44964</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44631</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45853</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45853</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45786</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45845</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>44928</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45786</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45623</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45489</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45587</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44896</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45912</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45623</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45489</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45912</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45666</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45387</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>44936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>44896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45917</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45917</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>44956</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45917</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45922</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44966</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45921</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45921</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45922</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45762</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45926</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>46076</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45574</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44883</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>44942</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46076</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46079</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45928</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46044</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>46084</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>46070</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46084</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>46055</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45439</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45936</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45936</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45936</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>46091</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>44945</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45937</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45343</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45239</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>44713</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45632</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45939</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>46098</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44704</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44689</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45946</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>46098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>46100</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>46100</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45560</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45580</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44704</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44704</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44701</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45947</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>46104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>46108</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>46108</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45954</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45954</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46108</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46111</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45958</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45957</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45957</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45957</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45957</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44959</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>46119</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45959</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45574</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>45966</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46127</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45965</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46126</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45075</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45972</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45446</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45973</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46127</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>46127</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>46127</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44696</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45314</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45973</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45127</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>46125</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45973</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45030</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>46134</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45092</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>46134</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>46134</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>46134</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>46134</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45982</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>46134</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45982</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45807</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45741</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45986</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45685</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45824</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45958</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45960</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45987</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45989</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45991</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45994</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45994</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45655</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>45994</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45748</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45812</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45999</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45950</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44924</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>46002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45961</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46002</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>46002</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45804</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45992</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45852</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45936</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>46139</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44980</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45184</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>46003</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45868</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45852</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46007</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45735</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44907</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>46008</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45833</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>46028</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>46010</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>46010</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46010</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>46010</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>45762</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>46008</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>46010</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>46008</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45173</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44732</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45987</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45046</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45229</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>46071</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45796</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>46126</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>45852</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>46139</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45818</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44909</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45135</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>46141</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>44735</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45239</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45226</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44620</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>46148</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>46148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46148</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>46148</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46147</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45245</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45541</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46154</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>44874</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>46153</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46153</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46155</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46155</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46160</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>45761</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44971</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>46161</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45080</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44965</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45851</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45851</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42194,7 +42194,7 @@
         <v>45851</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45852</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45812</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>45257</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>45677</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44491</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44964</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45121</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>46153</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45865</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>45785</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>46170</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>46171</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>44956</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46175</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44966</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45867</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46177</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46177</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45868</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45852</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45792</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>44965</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45635</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46178</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45582</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45639</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45174</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>46183</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45526</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45399</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45390</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>46185</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>45190</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45622</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>46188</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>46190</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>46190</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45394</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46190</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>46191</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>46195</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45632</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>46195</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>46195</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46195</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46195</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46196</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>46196</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45104</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>46196</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>46199</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>46199</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>46202</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45727</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44603</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46203</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>46203</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45189</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>46204</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46252</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46206</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46252</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44638</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45058</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>46252</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45224</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>44750</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45222</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45072</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44594</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46211</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44600</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>46212</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>46254</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>46254</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>46210</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46213</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>46212</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>46213</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>46257</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46213</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>44684</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>46257</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>44670</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46253</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45392</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>46260</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>46262</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45167</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>46262</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>44819</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44732</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45770</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>46219</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45244</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45203</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>45181</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>44804</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>44739</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>46265</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>46265</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>46266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50606,7 +50606,7 @@
         <v>46266</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>46268</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>46268</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>45366</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>46272</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45320</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>46230</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44781</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45275</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45736</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>46275</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45296</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46280</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45638</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45387</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>46282</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51789,7 +51789,7 @@
         <v>44865</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45470</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>44858</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>46239</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>46286</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>46148</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>44908</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>46286</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>46286</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>44972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45754</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>46287</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>44769</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>46244</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         <v>44597</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>46287</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45447</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>44909</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45580</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45344</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45401</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53435,7 +53435,7 @@
         <v>46248</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>45448</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>45022</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>44843</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45751</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>46248</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>46248</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>45772</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>44747</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>46248</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>46248</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>46248</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>44887</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>44847</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>44978</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45622</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>44518</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>44917</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>45310</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>44978</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45312</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45005</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45526</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55212,7 +55212,7 @@
         <v>45057</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>45105</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>44726</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45469</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45162</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>44984</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>44981</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>45252</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45252</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45439</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>45204</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45385</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45478</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>44929</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56239,7 +56239,7 @@
         <v>44945</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>45308</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45516</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45776</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>45357</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45785</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45527</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>45791</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56833,7 +56833,7 @@
         <v>44585</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45638</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45315</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45432</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45035</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45805</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>45982</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45660</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>46262</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>44651</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45061</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44595</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46021</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44964</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46295</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45758</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>46121</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>46161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45335</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45379</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44662</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45905</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>46071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>46101</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45294</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>45160</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45310</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45399</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45632</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>46188</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46188</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>46191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46211</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>46247</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45849</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45385</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>46089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44788</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>46003</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45621</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44846</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>46051</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45222</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>46054</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45965</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46127</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>46134</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45133</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>46148</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>46161</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>46280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45722</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>46171</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45741</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45310</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45784</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45789</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>44715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44481</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44580</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44708</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44886</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44824</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44627</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44504</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44734</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44480</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44859</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44551</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44865</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44581</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44543</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44704</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44788</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44648</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44648</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44491</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44672</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44631</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44749</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44627</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44945</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44858</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45252</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45080</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45189</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45580</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44847</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44491</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44907</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45005</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45394</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44620</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45173</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44704</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45527</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45961</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46003</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45344</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45224</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46002</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45622</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46008</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46008</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>46010</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>46010</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>46010</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>46010</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45447</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46014</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45022</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45791</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44769</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46017</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45910</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45783</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>46020</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45894</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44916</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44841</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>46027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45685</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44924</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45901</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46034</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45901</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>44739</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45538</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46036</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45909</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45908</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>46042</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46042</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45910</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46042</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45541</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45911</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45478</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45786</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45841</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44928</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45917</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45399</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45853</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45645</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45845</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45489</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45799</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46048</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45489</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45587</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45912</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45666</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45786</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45853</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44936</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45623</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46051</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46051</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45387</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46051</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45366</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45645</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>46051</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46055</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45921</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>46053</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45922</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46053</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46052</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45921</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>46052</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46053</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45928</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>45926</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45936</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45939</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45937</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45539</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45574</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45343</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45162</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45947</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>46076</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>46079</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44603</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46044</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44631</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>46055</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45957</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>44858</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45957</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45957</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46084</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45957</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45401</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45957</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46084</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45954</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45958</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45959</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44945</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46091</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45030</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45965</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44735</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44929</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45446</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45772</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>44942</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>46098</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>44518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45972</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>46100</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>46100</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45973</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45973</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46104</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45979</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45526</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46108</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45982</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46108</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45310</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45982</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>44837</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45987</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45958</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45960</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45393</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45989</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44965</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45991</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45582</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>44865</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45994</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44704</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44704</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45736</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46127</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>46125</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45138</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46000</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45314</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45770</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44887</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>46134</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46134</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45275</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>46134</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45390</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44670</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45804</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44843</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46071</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45632</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46126</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45824</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45992</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45833</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45748</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45987</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45936</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45868</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45950</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45807</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45637</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45812</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44972</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45851</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44684</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>45492</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46044</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45852</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45851</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45851</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45852</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>46139</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45852</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45847</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>46139</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45818</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44964</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45796</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44984</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45741</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>46028</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45852</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45057</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45785</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45635</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45312</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45330</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45320</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>46141</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45867</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45868</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45763</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>45184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45296</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>45852</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45105</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46146</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45222</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>46148</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>46148</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>46148</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>46153</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44956</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>44600</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46153</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44689</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>46155</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>46155</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>46155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45239</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45637</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46030</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46160</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45009</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44858</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45677</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45439</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45632</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>46153</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45257</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45239</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>46170</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46171</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45469</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45127</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45865</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45748</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>44726</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>46175</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>46176</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>46177</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46177</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>46177</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46178</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>44732</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44909</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46181</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>44959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46183</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>44853</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45574</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>46188</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>46188</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46185</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>46190</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>46190</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45265</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>46195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>46196</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46196</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>46195</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>46195</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>46196</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46196</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45751</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46199</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>46199</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45040</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46202</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>44781</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45400</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>44713</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>44781</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>44978</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>44750</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>46206</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44594</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46210</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44964</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44747</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45181</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>46212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>46211</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>46212</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>46213</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>46257</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>46213</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>46257</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46213</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44909</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45366</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>44964</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>46260</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45560</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45135</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>46262</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46265</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45229</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>44978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>46266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46268</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46268</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45761</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45058</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>44956</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45639</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>44908</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>44971</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45470</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44597</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45580</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>44874</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>46280</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44701</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46239</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>45244</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45385</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46244</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>44696</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46287</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46148</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>46286</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>46286</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>46286</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45439</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45387</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46248</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45387</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>46248</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>44792</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>45762</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>45104</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45072</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46248</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46295</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>46252</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54021,7 +54021,7 @@
         <v>46294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>46252</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45655</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>46297</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46297</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46248</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>46252</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>46253</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>46254</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54786,7 +54786,7 @@
         <v>46148</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>45174</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54932,7 +54932,7 @@
         <v>46254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>46297</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44980</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55161,7 +55161,7 @@
         <v>44981</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45439</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>44732</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>45204</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45754</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45203</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45075</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>44883</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45167</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44917</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>44804</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45046</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45392</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45448</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45762</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45727</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>45092</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>45390</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45033</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45638</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45776</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45516</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>45308</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45357</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45785</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45638</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45315</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>44585</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45432</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45035</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45805</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>45982</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45660</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>46262</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>44651</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45061</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44595</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46021</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44964</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46295</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45758</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>46121</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>46161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45335</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45379</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44662</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45905</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>46071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>46101</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45294</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>45160</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45310</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45399</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45632</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>46188</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46188</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>46191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46211</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>46247</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45849</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45385</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>46089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44788</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>46003</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45621</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44846</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>46051</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45222</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>46054</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45965</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46127</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>46134</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45133</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>46148</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>46161</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>46280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45722</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>46171</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45741</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45310</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45784</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45789</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>44715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44481</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44580</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44708</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44886</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44824</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44627</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44504</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44734</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44480</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44859</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44551</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44865</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44581</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44543</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44704</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44788</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44648</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44648</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44491</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44672</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44631</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44749</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44627</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44945</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44858</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45252</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45080</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45189</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45580</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44847</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44491</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44907</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45005</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45394</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44620</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45173</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44704</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45527</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45961</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46003</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45344</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45224</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46002</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45622</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46008</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46008</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>46010</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>46010</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>46010</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>46010</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45447</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46014</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45022</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45791</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44769</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46017</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45910</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45783</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>46020</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45894</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44916</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44841</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>46027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45685</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44924</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45901</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46034</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45901</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>44739</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45538</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46036</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45909</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45908</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>46042</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46042</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45910</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46042</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45541</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45911</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45478</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45786</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45841</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44928</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45917</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45399</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45853</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45645</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45845</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45489</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45799</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46048</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45489</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45587</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45912</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45666</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45786</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45853</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44936</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45623</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>46051</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46051</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45387</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46051</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45366</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45645</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>46051</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46055</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45921</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>46053</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45922</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46053</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46052</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45921</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>46052</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46053</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45928</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>45926</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45936</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45939</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45937</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45539</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45574</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45343</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45162</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45947</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>46076</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>46079</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44603</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46044</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44631</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>46055</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45957</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>44858</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45957</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45957</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46084</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45957</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45401</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45957</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46084</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45954</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45958</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45959</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44945</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46091</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45030</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45965</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44735</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44929</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45446</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45772</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>44942</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>46098</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>44518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45972</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>46100</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>46100</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45973</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45973</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46104</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45979</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45526</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46108</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45982</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46108</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45310</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45982</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>44837</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45987</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45958</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45960</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45393</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45989</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44965</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45991</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45582</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>44865</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45994</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44704</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44704</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45736</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46127</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>46125</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45138</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46000</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45314</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45770</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44887</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>46134</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46134</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45275</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>46134</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45390</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44670</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45804</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44843</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46071</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45632</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46126</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45824</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45992</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45833</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45748</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45987</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45936</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45868</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45950</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45807</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45637</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45812</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44972</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45851</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44684</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>45492</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46044</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45852</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45851</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45851</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45852</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>46139</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45852</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45847</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>46139</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45818</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44964</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45796</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44984</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45741</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>46028</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45852</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45057</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45785</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45635</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45312</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45330</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45320</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>46141</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45867</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45868</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45763</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>45184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45296</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>45852</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45105</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46146</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45222</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>46148</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>46148</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>46148</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>46153</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44956</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>44600</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46153</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44689</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>46155</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>46155</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>46155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45239</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45637</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46030</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46160</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45009</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44858</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45677</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45439</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45632</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>46153</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45257</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45239</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>46170</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46171</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45469</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45127</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45865</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45748</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>44726</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>46175</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>46176</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>46177</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>46177</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>46177</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46178</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>44732</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44909</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46181</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>44959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46183</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>44853</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45574</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>46188</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>46188</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46185</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>46190</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>46190</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45265</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>46195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>46196</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46196</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>46195</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>46195</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>46196</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46196</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45751</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46199</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>46199</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45040</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46202</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>44781</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45400</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>44713</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>44781</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>44978</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>44750</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>46206</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44594</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46210</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44964</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44747</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45181</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>46212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>46211</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>46212</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>46213</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>46257</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>46213</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>46257</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46213</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44909</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45366</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>44964</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>46260</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45560</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45135</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>46262</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46265</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45229</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>44978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>46266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46268</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46268</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45761</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45058</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>44956</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45639</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>44908</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>44971</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45470</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44597</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45580</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>44874</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>46280</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44701</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46239</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>45244</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45385</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46244</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>44696</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46287</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46148</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>46286</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>46286</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>46286</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45439</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45387</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46248</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45387</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>46248</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>44792</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>45762</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>45104</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45072</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46248</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46295</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>46252</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54021,7 +54021,7 @@
         <v>46294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>46252</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45655</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>46297</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46297</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46248</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>46252</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>46253</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>46254</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54786,7 +54786,7 @@
         <v>46148</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>45174</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54932,7 +54932,7 @@
         <v>46254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>46297</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44980</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55161,7 +55161,7 @@
         <v>44981</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45439</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>44732</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>45204</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45754</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45203</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45075</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>44883</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45167</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44917</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>44804</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45046</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45392</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45448</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45762</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45727</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>45092</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>45390</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45033</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45638</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45776</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45516</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>45308</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45357</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45785</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45638</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45315</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>44585</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45432</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45035</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45805</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>45982</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44651</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45061</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>46052</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44595</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45722</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46295</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45335</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45853</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45379</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>46121</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45966</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45758</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>45905</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45294</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45160</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>45142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>46101</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45966</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45965</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45385</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45548</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45399</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45818</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>46191</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>46247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45849</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>46301</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>46089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44788</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45741</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44950</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45748</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45674</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45965</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45645</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45133</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46111</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46127</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>46134</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44937</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>46010</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45722</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44978</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46054</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>46206</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46213</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>46280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>46171</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46304</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44481</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44580</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44708</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44504</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44790</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44491</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44742</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44636</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44859</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44865</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44672</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44788</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44704</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44701</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44648</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44648</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44728</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44548</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45330</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45312</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45245</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45390</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45541</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45005</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45161</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44874</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45526</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45057</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44781</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45387</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44726</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45469</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45162</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45761</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44853</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>44971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44792</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44916</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45763</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44837</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45080</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45251</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45033</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45253</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45252</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44858</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44491</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45763</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44964</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45040</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45121</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44956</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45685</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45896</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45204</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45385</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45478</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45901</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45538</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45902</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45901</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44966</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45748</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44945</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45908</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45908</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45308</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45909</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45911</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45393</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45635</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45138</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45357</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45582</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45841</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45853</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45853</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45639</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45174</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45489</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45071</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45912</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45399</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45623</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45489</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45666</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45390</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45400</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>44896</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44631</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45917</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45917</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45922</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45922</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44956</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45921</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45785</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45921</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45922</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44966</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45394</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45762</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45632</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45574</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44883</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44942</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45791</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45928</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45511</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45119</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45439</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>44945</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45799</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44603</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45189</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45239</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44713</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45936</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45526</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45366</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45387</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44704</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44689</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45560</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45580</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45058</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44704</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>44704</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>44701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45224</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45343</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45222</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45072</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44594</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44600</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45946</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45446</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44959</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44684</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45392</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45075</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45954</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45954</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45637</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45958</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44696</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45127</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45030</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>44819</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>44732</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45770</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45966</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45244</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45181</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45685</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45972</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44804</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>44739</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45973</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45851</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45973</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45851</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45973</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45812</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45655</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>44924</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45867</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45868</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45852</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45366</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45979</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45526</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>44907</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45762</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>44732</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45320</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44781</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45275</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>45736</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45982</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45046</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45982</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46098</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45229</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46098</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46100</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>46100</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45135</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45638</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45387</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45986</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45239</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>44865</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45470</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44858</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45958</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>46108</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>46108</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45960</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45987</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46108</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44620</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>46111</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45989</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45991</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45957</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>46119</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45994</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45994</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>44908</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45994</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46127</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44972</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45754</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46126</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45999</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46002</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>46127</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>46127</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>46125</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44769</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>44597</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>45961</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45961</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>46134</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46134</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46134</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46134</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46003</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45741</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45447</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>44909</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45279</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45580</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46007</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45344</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45448</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45022</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>44843</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>46008</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>46010</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46010</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>46010</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>46010</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>46009</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46010</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45847</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46008</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45772</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>44747</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45748</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46017</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45783</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45951</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45910</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>46020</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45812</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46027</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>44847</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44978</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45950</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>45622</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45804</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45992</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45852</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45936</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46034</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46139</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45184</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45868</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46034</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45735</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>45833</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>46036</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>46028</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44518</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>46044</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46042</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>46042</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46042</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45310</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>46071</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>45796</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>46126</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45852</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>46139</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45818</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>44978</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>46048</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>46141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46051</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46052</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>46051</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>46051</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>46051</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>46051</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>46052</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>46051</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>46053</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>46055</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46055</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>46053</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>46055</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46053</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45226</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46146</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>46147</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>46076</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>46153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>46076</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>46079</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>46044</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>46084</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48188,7 +48188,7 @@
         <v>46070</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>46084</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>46055</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46155</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46155</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>46091</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>46030</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>46161</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45677</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46153</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45865</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>46170</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46171</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>46176</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>46175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>46177</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>46177</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>46181</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>46178</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46183</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46188</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46188</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46190</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46191</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>46195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>46195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>46195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>46195</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>46196</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>46196</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>46196</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>46196</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>46199</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>46199</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>46202</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>46203</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46203</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46204</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44750</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>46210</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46213</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>46212</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46213</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46213</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46219</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46265</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>46265</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46266</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46266</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>46268</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>46230</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>46275</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46239</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>46286</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>46148</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>46286</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>46286</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>46244</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46248</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>46294</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>46248</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>46248</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46295</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>46252</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>46295</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>46252</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>46253</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>46195</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54550,7 +54550,7 @@
         <v>46297</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46257</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46257</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46254</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>46254</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>46282</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46297</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>46252</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>46148</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46148</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>46248</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>46212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45965</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45786</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>46177</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46304</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>46304</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>46262</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>46262</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>46303</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>46303</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>46190</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>44585</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45638</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45315</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45432</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45035</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>45805</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45982</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44651</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45061</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>46052</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44595</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45722</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46295</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45335</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45853</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45379</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>46121</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45966</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45758</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>45905</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45294</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45160</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>45142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>46101</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45966</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45965</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45385</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45548</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45399</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45818</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>46191</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>46247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45849</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>46301</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>46089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44788</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45741</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44950</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45748</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45674</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45965</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45645</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45133</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46111</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46127</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>46134</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44937</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>46010</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45722</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44978</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46054</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>46206</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46213</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>46280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>46171</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46304</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44481</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44580</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44708</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44504</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44790</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44491</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44742</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44636</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44859</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44865</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44672</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44788</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44704</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44701</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44648</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44648</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44728</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44548</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45330</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45312</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45245</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45390</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45541</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45005</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45161</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44874</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45526</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45057</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44781</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45387</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44726</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45469</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45162</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45761</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44853</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>44971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44792</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44916</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45763</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44837</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45080</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45251</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45033</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45253</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45252</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44858</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44491</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45763</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44964</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45040</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45121</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44956</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45685</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45896</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45204</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45385</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45478</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45901</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45538</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45902</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45901</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44966</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45748</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44945</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45908</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45908</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45308</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45909</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45911</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45393</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45635</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45138</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45357</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45582</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45841</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45853</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45853</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45639</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45174</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45489</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45071</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45912</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45399</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45623</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45489</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45666</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45390</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45400</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>44896</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44631</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45917</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45917</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45922</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45922</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44956</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45921</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45785</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45921</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45922</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44966</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45394</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45762</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45632</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45574</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44883</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44942</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45791</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45928</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45511</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45119</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45439</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>44945</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45799</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44603</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45189</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45239</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44713</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45936</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45526</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45366</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45387</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44704</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44689</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45560</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45580</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45058</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44704</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>44704</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>44701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45224</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45343</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45222</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45072</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44594</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44600</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45946</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45446</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44959</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44684</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45392</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45075</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45954</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45954</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45637</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45958</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44696</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45127</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45030</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>44819</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>44732</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45770</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45966</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45244</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45181</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45685</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45972</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44804</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>44739</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45973</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45851</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45973</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45851</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45973</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45812</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45655</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>44924</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45867</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45868</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45852</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45366</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45979</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45526</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>44907</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45762</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>44732</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45320</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44781</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45275</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>45736</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45982</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45046</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45982</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46098</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45229</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46098</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46100</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>46100</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45135</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45638</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45387</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45986</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45239</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>44865</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45470</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44858</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45958</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>46108</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>46108</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45960</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45987</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46108</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44620</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>46111</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45989</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45991</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45957</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>46119</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45994</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45994</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>44908</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45994</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46127</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44972</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45754</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46126</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45999</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46002</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>46127</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>46127</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>46127</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>46125</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44769</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>44597</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>45961</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45961</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>46134</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46134</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46134</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46134</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46003</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45741</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45447</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>44909</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45279</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45580</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46007</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45344</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45448</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45022</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>44843</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>46008</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>46010</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46010</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>46010</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>46010</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>46009</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46010</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45847</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46008</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45772</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>44747</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45748</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46017</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45783</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45951</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45910</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>46020</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45812</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46027</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>44847</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44978</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45950</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>45622</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45804</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45992</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45852</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45936</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46034</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46139</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45184</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45868</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46034</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45735</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>45833</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>46036</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>46028</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44518</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>46044</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46042</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>46042</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46042</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45310</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>46071</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>45796</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>46126</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45852</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>46139</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45818</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>44978</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>46048</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>46141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46051</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46052</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>46051</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>46051</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>46051</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>46051</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>46052</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>46051</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>46053</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>46055</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46055</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>46053</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>46055</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46053</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45226</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46146</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>46147</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>46076</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>46153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>46076</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>46079</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>46044</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>46084</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48188,7 +48188,7 @@
         <v>46070</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>46084</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>46055</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46155</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46155</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>46091</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>46030</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>46161</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45677</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46153</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45865</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>46170</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46171</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>46176</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>46175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>46177</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>46177</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>46181</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>46178</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46183</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46188</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46188</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46190</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46191</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>46195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>46195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>46195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>46195</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>46196</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>46196</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>46196</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>46196</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>46199</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>46199</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>46202</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>46203</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46203</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46204</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44750</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>46210</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46213</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>46212</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46213</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46213</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46219</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46265</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>46265</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46266</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46266</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>46268</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>46230</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>46275</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46239</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>46286</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>46148</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>46286</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>46286</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>46244</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46248</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>46294</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>46248</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>46248</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46295</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>46252</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>46295</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>46252</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>46253</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>46195</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54550,7 +54550,7 @@
         <v>46297</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46257</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46257</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46254</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>46254</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>46282</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46297</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>46252</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>46148</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46148</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>46248</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>46212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45965</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45786</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>46177</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46304</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>46304</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>46262</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>46262</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>46303</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>46303</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>46190</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>44585</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45638</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45315</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45432</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45035</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>45805</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45982</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45660</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44970</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>45181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45061</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44595</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>46295</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44551</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45840</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44804</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45966</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45722</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45758</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>46121</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45335</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45379</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44587</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44662</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45294</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45142</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45965</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>46071</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>46101</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45160</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45632</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46191</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44862</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>46247</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45849</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>46253</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45548</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45964</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46301</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45818</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>46311</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44788</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44950</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44846</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45133</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>46161</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>46051</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46054</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>46181</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>46134</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45722</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46206</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>46213</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45741</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45310</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46171</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>46304</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45818</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44580</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44708</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44824</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44504</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44627</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44859</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44551</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44865</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44581</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44704</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44701</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>44548</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>44742</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44788</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44648</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>44648</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44491</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44636</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>44672</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44631</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44728</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44749</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44627</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>44627</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>44945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45252</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>44858</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>45252</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>44965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45189</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>44491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45080</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45580</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44847</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44907</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45005</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44704</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45173</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44620</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45344</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45622</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45224</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44769</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45447</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45022</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>44916</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44853</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44739</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>44638</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45478</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45399</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>44966</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45574</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45162</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>44603</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44631</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45401</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45030</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44945</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44735</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44518</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45772</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45526</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45310</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44837</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45987</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45868</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45950</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45812</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45393</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>46044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45582</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45852</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44865</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>44704</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45847</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44704</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>46139</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45736</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45818</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45796</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45735</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45138</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45121</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45685</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45770</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44887</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>46028</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45852</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45226</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45275</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46141</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45390</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45538</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>46029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44670</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45748</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>44843</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45910</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44896</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44896</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44928</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45917</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45853</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45917</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45845</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45489</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45912</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>46146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45489</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45071</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45587</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45853</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44936</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45917</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45623</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45637</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>46147</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45921</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45922</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45922</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45265</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45921</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44684</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45928</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45926</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45936</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45939</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45937</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>44964</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46153</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>44984</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45057</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45635</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46155</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45946</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45312</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46155</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46154</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45957</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45330</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45957</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45957</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45320</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46155</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45957</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45957</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45954</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45958</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45959</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45763</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45965</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>46030</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45296</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45966</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45105</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46160</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45222</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45973</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45973</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44956</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>44600</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45982</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>44689</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45982</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45987</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45958</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45986</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45960</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45960</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45989</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45677</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45637</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45991</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45957</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45994</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45994</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45994</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45009</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45999</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44858</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45961</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45961</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46153</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>46003</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46170</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45439</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>46002</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>46002</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>46007</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45632</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45257</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45469</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46009</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>46010</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45127</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46010</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>46010</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46010</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45748</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44726</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46014</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45865</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>46017</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44732</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45910</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45783</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46020</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44966</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44909</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>46027</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44959</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44853</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45574</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>46034</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>46034</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>46175</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46176</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>46177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>46036</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>46178</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>46042</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>46043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>46042</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>46042</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>46048</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>46048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>46051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>46051</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>46051</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46051</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46051</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46181</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46051</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46055</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>46055</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46053</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46053</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46052</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46052</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46053</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46055</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>46183</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45751</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45040</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46188</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46188</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>44781</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>46185</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>46076</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45400</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>44713</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44781</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>46079</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46044</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46070</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>44978</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>46055</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>46084</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>46084</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46190</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>46190</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>44747</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>46091</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46191</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>46191</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45181</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>46098</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46098</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>46100</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>46195</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>46100</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>46196</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46104</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46195</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>44909</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45366</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44964</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46196</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46196</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45245</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45560</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46108</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>46108</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>46108</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45229</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>44978</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>46119</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46126</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46127</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46127</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>46127</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46127</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45761</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>46125</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45314</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>44956</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45639</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>46134</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46134</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>44908</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46134</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45470</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>44597</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45804</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45580</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>44874</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46071</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>46126</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45824</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44701</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45833</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46561,7 +46561,7 @@
         <v>45748</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44750</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46206</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46210</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45244</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45190</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>46212</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>46211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45385</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>44696</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46213</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>46213</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>46213</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>46219</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45439</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>46272</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45387</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>46230</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45387</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46275</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>44792</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45762</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>45104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45072</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48378,7 +48378,7 @@
         <v>45655</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>46239</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45174</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>46244</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>44980</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44981</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>46287</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46287</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45439</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46286</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46286</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>44732</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45204</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45754</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>45203</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45075</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>46248</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>46248</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>46248</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44883</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>46248</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46295</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>46294</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46252</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>46295</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45167</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>44917</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45046</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45392</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>46252</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45448</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>46297</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>46297</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45727</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>46248</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45092</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>46252</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>46253</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51860,7 +51860,7 @@
         <v>46282</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45390</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45033</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52084,7 +52084,7 @@
         <v>46254</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>46148</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46254</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46297</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>45638</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45965</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45776</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>45516</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>45308</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45357</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52839,7 +52839,7 @@
         <v>46148</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46212</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46195</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>46257</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45785</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>46257</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45527</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45786</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>45791</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>46303</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45119</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45203</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45511</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>46304</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45645</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45526</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46262</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45799</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>46190</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45387</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45366</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>46265</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>46266</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45645</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46266</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>46309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>46309</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46268</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45446</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46310</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>46311</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45851</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45812</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>45852</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45851</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45851</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45785</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45867</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45868</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45852</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45526</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>45638</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>45315</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44585</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56755,7 +56755,7 @@
         <v>45432</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56833,7 +56833,7 @@
         <v>45035</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45805</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45982</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45940</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45660</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44970</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>45181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45061</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45035</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45660</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46191</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44579</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44595</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45208</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>46295</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44551</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45840</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44804</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45966</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45722</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45758</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>46121</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45335</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45379</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44587</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44662</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45294</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45142</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45966</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45965</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>46071</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>46101</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45160</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45632</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46191</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44862</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>46247</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45849</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>46253</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45548</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45964</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46301</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45818</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>46311</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44579</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44756</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44788</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44656</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44950</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44846</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45133</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>46161</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>46051</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46054</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>46181</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>46134</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45722</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46206</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>46213</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45741</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45310</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46171</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>46304</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45818</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44837</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44580</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44708</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44708</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44824</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44504</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44627</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44859</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44551</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44865</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44581</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44704</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44701</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>44548</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>44742</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44788</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44648</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>44648</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44491</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44636</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>44672</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44631</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44728</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44749</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44627</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>44627</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>44945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45252</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>44858</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>45252</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>44965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45189</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>44491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45080</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45580</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44847</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44907</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45005</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44704</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45173</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44620</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45344</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45622</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45224</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44769</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45447</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45022</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>44916</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44853</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44739</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>44638</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45478</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45399</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>44966</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45574</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45162</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>44603</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44631</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45401</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45030</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44945</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44735</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44518</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45772</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45526</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45310</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44837</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45987</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45868</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45950</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45812</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45393</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>46044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45582</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45852</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44865</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>44704</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45847</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44704</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>46139</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45736</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45818</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45796</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45735</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45138</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45121</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45685</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45770</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44887</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>46028</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45852</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45226</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45275</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46141</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45390</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45538</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>46029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44670</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45748</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>44843</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45910</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44896</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44896</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44928</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45917</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45853</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45917</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45845</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45489</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45912</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>46146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45489</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45071</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45587</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45853</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44936</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45917</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45623</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45637</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>46147</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45921</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45922</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45922</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45265</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45921</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44684</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45928</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45926</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45936</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45936</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45939</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45937</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>44964</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46153</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>44984</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45057</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45635</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46155</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45946</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45312</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46155</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46154</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45957</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45330</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45957</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45957</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45320</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46155</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45957</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45957</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45954</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45958</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45959</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45763</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45965</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>46030</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45296</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45966</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45105</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46160</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45222</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45973</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45973</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44956</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>44600</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45982</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>44689</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45982</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45987</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45958</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45986</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45960</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45960</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45989</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45677</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45637</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45991</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45957</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45994</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45994</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45994</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45009</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45999</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44858</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45961</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45961</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46153</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>46003</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46170</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45439</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>46002</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>46002</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>46007</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45632</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45257</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45469</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46009</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>46010</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45127</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46010</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>46010</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46010</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45748</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44726</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46014</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45865</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>46017</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44732</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45910</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45783</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46020</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44966</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44909</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>46027</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44959</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44853</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45574</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>46034</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>46034</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>46175</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46176</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46177</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>46177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>46036</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>46178</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>46042</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>46043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>46042</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>46042</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>46048</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>46048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>46051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>46051</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>46051</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46051</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46051</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46181</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46051</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46055</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>46055</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46053</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46053</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46052</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46052</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46053</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46055</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>46183</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45751</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45040</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46188</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46188</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>44781</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>46185</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>46076</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45400</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>44713</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44781</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>46079</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46044</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46070</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>44978</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>46055</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>46084</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>46084</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46190</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>46190</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>44747</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>46091</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46191</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>46191</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45181</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>46098</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46098</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>46100</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>46195</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>46100</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>46196</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46104</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46195</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>44909</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45366</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44964</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46196</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46196</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45245</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45560</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46108</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>46108</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>46108</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45229</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>44978</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>46119</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46126</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46127</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46127</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>46127</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46127</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45761</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>46125</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45314</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>44956</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45639</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>46134</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46134</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>44908</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46134</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45470</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>44597</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45804</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45580</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>44874</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46071</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>46126</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45824</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44701</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45833</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46561,7 +46561,7 @@
         <v>45748</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44750</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46206</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46210</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45244</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45190</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>46212</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>46211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45385</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>44696</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46213</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>46213</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>46213</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>46219</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45439</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>46272</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45387</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>46230</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45387</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46275</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>44792</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45762</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>45104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45072</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48378,7 +48378,7 @@
         <v>45655</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>46239</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45174</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>46244</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>44980</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44981</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>46287</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46287</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45439</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46286</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46286</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>44732</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45204</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45754</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>45203</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45075</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>46248</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>46248</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>46248</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44883</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>46248</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46295</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>46294</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46252</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>46295</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45167</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>44917</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45046</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45392</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>46252</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45448</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>46297</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>46297</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45727</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>46248</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45092</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>46252</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>46253</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51860,7 +51860,7 @@
         <v>46282</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45390</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45033</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52084,7 +52084,7 @@
         <v>46254</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>46148</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46254</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46297</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>45638</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45965</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45776</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>45516</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>45308</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45357</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52839,7 +52839,7 @@
         <v>46148</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46212</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46195</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>46257</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45785</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>46257</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45527</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45786</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>45791</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>46303</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45119</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45203</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45511</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>46304</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45645</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45526</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46262</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45799</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>46190</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45387</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45366</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>46265</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>46266</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45645</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46266</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>46309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>46309</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46268</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45446</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46310</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>46311</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45851</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45812</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>45852</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45851</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45851</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45785</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45867</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45868</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45852</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45526</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>45638</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>45315</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44585</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56755,7 +56755,7 @@
         <v>45432</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56833,7 +56833,7 @@
         <v>45035</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45805</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45982</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44579</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45940</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44651</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>45181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>46311</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>45061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45035</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>44950</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45492</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45660</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44595</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>44651</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45208</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>44551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46295</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>46089</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>45853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45966</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45758</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>46121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>46314</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>45379</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45310</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46010</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46286</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46101</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45142</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45632</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>46191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>46247</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45849</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45818</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45964</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46301</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45281</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>46265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>46311</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44579</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44827</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44756</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44788</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44684</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44755</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>46161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44846</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44978</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45973</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46213</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46280</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45789</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45573</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>46051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>46054</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45818</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>46171</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45645</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>46111</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>46304</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>46127</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>46134</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44937</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45741</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45222</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>46318</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>46148</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45748</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45674</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45133</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45310</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45274</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44560</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44713</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44516</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44515</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44715</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44580</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>44708</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44708</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44824</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44504</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44627</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>44790</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44517</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44734</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44859</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>44551</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44865</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44543</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44704</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44701</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44648</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44648</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44636</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44672</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44631</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>44728</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44627</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45447</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45279</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45580</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44781</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45387</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45344</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45448</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45022</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45685</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>44843</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45751</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45896</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45033</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45253</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45772</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45538</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45902</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44747</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45901</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45901</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45901</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45330</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45748</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>46030</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45910</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44847</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45909</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>46161</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45853</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45853</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45623</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45489</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45587</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45071</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45912</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45489</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45666</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>44936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44896</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45917</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>45917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45922</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45921</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44518</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45921</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45677</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45926</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44841</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45390</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45928</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45865</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46171</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45310</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45936</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45936</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45937</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44858</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45939</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45312</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45946</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45005</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44853</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>46177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45748</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44916</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45763</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44837</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45251</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45526</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46181</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45057</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44726</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45954</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45439</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45957</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>46188</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44984</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45966</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46190</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46191</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46195</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45252</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46195</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46195</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>46196</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45973</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46199</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46199</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44858</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>46203</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45982</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45982</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45439</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45986</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45204</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45385</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45478</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45958</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>44929</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45960</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45987</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44750</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46211</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45989</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46213</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45991</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>46212</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>46213</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45763</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46213</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>45994</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>45994</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45040</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>44945</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46219</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45308</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45516</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45776</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45961</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45357</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46230</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46010</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46010</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>46280</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>46014</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45785</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45527</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>46017</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45783</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45910</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>46020</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45265</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>46027</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>46030</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>46286</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>46034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>46034</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>45791</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>46036</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45511</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>46148</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45119</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>46286</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45203</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46042</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46042</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>46042</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46244</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46043</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46048</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45526</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45366</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45387</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46052</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>46051</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46051</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46051</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>46051</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>46052</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>46051</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>46053</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46055</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>46055</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46053</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>46055</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46053</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45343</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46248</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46248</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>44853</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46248</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46248</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46294</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45446</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46294</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46248</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>46248</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46076</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>46076</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>46079</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46295</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>46252</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>46295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>46252</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46044</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46084</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46070</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46257</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46257</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46084</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>46254</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46254</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>46282</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>46091</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>46297</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46297</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46252</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46098</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46098</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46100</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46248</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46212</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46100</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45965</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>46104</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45851</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>45851</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45852</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45812</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>46108</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46108</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46108</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>46111</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45785</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45786</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46177</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45867</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45868</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45852</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45526</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>46304</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46127</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46304</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>46126</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>46303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>46303</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46127</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45314</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>46125</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>46262</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>46262</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>46134</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>45539</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46134</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46134</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>46134</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>46190</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>46134</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>46134</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>45393</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45138</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>45741</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45824</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45400</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>46266</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>46266</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>44964</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45847</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>44631</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45748</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>46309</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44956</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45812</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45950</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>46314</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>44966</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45804</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46268</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45852</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45936</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>46268</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45762</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>46139</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>46310</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45868</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45852</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45735</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45833</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46028</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45574</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>44883</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>46044</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>44942</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46029</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45987</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46315</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46315</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>46071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>45796</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>46126</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45852</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>46139</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45818</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>46141</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45439</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>46317</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46317</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>44945</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45226</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>46317</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45239</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44713</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>46275</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>46146</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45632</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>46317</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>46317</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>44704</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>46147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>44689</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45560</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45580</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46154</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44704</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44704</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>46153</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44701</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>46153</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>46160</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>45009</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>44959</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45574</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>45075</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45637</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45637</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>44696</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45127</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51404,7 +51404,7 @@
         <v>44964</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45030</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45092</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45685</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45655</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>44924</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>44980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>44907</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45762</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45173</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44732</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45046</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45229</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52378,7 +52378,7 @@
         <v>44909</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52451,7 +52451,7 @@
         <v>45135</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>44735</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45239</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>44620</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45245</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45541</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>45161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>44874</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45761</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>44971</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45080</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44965</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45257</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>44964</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45121</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>44956</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>44966</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>44965</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45635</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53858,7 +53858,7 @@
         <v>45582</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>45639</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
         <v>45399</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>45390</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45190</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45622</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45394</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45632</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>45104</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>45170</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45727</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44603</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>45189</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>44638</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45058</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>45224</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>45222</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55275,7 +55275,7 @@
         <v>44594</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>44600</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>44684</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44670</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45392</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45167</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44819</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>44732</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45770</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>45244</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45203</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>45181</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>44804</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>44739</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56351,7 +56351,7 @@
         <v>45366</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>45320</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>44781</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45275</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>45736</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45296</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56794,7 +56794,7 @@
         <v>45638</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45387</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>44865</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45470</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>44858</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>44908</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>44972</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45754</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>44769</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>44597</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57529,7 +57529,7 @@
         <v>44585</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45638</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45315</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>45432</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>45035</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57919,7 +57919,7 @@
         <v>45805</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>45982</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -601,7 +601,7 @@
         <v>45659</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44496</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44579</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45940</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44651</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>44970</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>45181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>46311</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>45061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45035</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>44950</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45492</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45660</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46261</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44595</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46021</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>44651</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45208</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>44551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46295</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>46089</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>45853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45966</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45758</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>46121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>46314</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>45379</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45310</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46010</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46286</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46101</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45142</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45632</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>46191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>46247</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45849</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45818</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45964</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46301</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45281</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>46265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>46311</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44579</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44827</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44756</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44788</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44684</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44755</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>46161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44846</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44978</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45973</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46213</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46280</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45789</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45573</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>46051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>46054</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45818</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>46171</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45645</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>46111</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>46304</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>46127</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>46134</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44937</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45741</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45222</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>46318</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>46148</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45748</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45674</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45133</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45310</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45274</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44560</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44713</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44516</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44515</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44715</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44580</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>44708</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44708</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44824</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44504</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44627</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>44790</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44517</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44734</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44859</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>44551</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44865</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44543</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44704</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44701</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44648</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44648</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44636</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44672</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44631</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>44728</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44627</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45447</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45279</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45580</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44781</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45387</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45344</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45448</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45022</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45685</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>44843</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45751</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45896</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45033</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45253</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45772</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45538</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45902</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44747</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45901</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45901</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45901</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45330</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45748</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>46030</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45910</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44847</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45909</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>46161</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45853</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45853</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45623</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45489</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45587</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45071</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45912</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45489</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45666</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>44936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44896</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45917</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>45917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45922</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45921</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44518</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45921</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45677</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45926</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44841</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45390</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45928</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45865</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46171</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45310</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45936</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45936</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45937</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44858</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45939</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45312</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45946</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45005</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44853</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>46177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45748</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44916</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45763</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44837</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45251</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45526</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46181</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45057</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44726</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45954</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45439</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45957</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>46188</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44984</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45966</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46190</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46191</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46195</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45252</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46195</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46195</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>46196</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45973</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46199</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46199</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44858</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>46203</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45982</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45982</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45439</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45986</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45204</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45385</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45478</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45958</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>44929</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45960</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45987</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44750</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46211</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45989</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46213</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45991</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>46212</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>46213</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45763</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46213</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>45994</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>45994</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45040</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>44945</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46219</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45308</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45516</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45776</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45961</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45357</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46230</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46010</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46010</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>46280</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>46014</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45785</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45527</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>46017</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45783</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45910</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>46020</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45265</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>46027</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>46030</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>46286</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>46034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>46034</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>45791</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>46036</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45511</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>46148</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45119</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>46286</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45203</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46042</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46042</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>46042</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46244</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46043</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46048</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45526</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45366</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45387</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46052</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>46051</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46051</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46051</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>46051</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>46052</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>46051</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>46053</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46055</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>46055</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46053</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>46055</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46053</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45343</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46248</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46248</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>44853</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46248</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46248</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46294</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45446</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46294</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46248</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>46248</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46076</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>46076</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>46079</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46295</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>46252</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>46295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>46252</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46044</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46084</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46070</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46257</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46257</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46084</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>46254</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46254</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>46282</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>46091</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>46297</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46297</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46252</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46098</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46098</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46100</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46248</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46212</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46100</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45965</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>46104</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45851</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>45851</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45852</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45812</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>46108</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46108</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46108</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>46111</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45785</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45786</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46177</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45867</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45868</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45852</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45526</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>46304</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46127</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46304</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>46126</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>46303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>46303</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46127</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45314</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>46125</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>46262</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>46262</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>46134</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>45539</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46134</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46134</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>46134</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>46190</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>46134</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>46134</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>45393</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45138</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>45741</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45824</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45400</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>46266</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>46266</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>44964</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45847</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>44631</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45748</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>46309</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44956</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45812</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45950</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>46314</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>44966</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45804</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46268</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45852</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45936</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>46268</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45762</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>46139</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>46310</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45868</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45852</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45735</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45833</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46028</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45574</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>44883</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>46044</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>44942</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46029</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45987</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46315</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46315</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>46071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>45796</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>46126</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45852</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>46139</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45818</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>46141</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45439</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>46317</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46317</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>44945</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45226</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>46317</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45239</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44713</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>46275</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>46146</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45632</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>46317</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>46317</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>44704</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>46147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>44689</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45560</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45580</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46154</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44704</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44704</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>46153</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44701</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>46153</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>46160</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>45009</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>44959</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45574</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>45075</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45637</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45637</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>44696</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45127</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51404,7 +51404,7 @@
         <v>44964</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45030</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45092</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45685</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45655</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>44924</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>44980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>44907</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45762</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45173</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>44732</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45046</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45229</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52378,7 +52378,7 @@
         <v>44909</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52451,7 +52451,7 @@
         <v>45135</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>44735</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45239</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>44620</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45245</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45541</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>45161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>44874</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45761</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>44971</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45080</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44965</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45257</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>44964</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45121</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>44956</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>44966</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>44965</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45635</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53858,7 +53858,7 @@
         <v>45582</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>45639</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
         <v>45399</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>45390</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45190</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45622</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45394</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45632</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>45104</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>45170</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45727</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44603</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>45189</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>44638</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45058</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>45224</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>45222</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55275,7 +55275,7 @@
         <v>44594</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>44600</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>44684</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44670</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45392</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45167</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44819</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>44732</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45770</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>45244</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45203</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>45181</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>44804</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>44739</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56351,7 +56351,7 @@
         <v>45366</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>45320</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>44781</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45275</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>45736</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45296</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56794,7 +56794,7 @@
         <v>45638</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45387</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>44865</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45470</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>44858</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>44908</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>44972</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45754</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>44769</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>44597</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57529,7 +57529,7 @@
         <v>44585</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45638</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45315</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>45432</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>45035</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57919,7 +57919,7 @@
         <v>45805</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>45982</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
